--- a/debug_bbox2/layout_ranking_report.xlsx
+++ b/debug_bbox2/layout_ranking_report.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout Rankings Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relational Details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -66,7 +68,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +97,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -130,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -151,15 +159,27 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,27 +601,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM Layout Quality &amp; Walkability Benchmark Report</t>
+          <t xml:space="preserve">  ROOM Layout Quality &amp; Relational Accuracy Benchmark Report</t>
         </is>
       </c>
     </row>
@@ -609,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Runs Analyzed: 2  |  Metrics: Furniture Overlaps, OBB Overlap Area, Out-of-Bounds Protrusions, Free Floor %, Walkability</t>
+          <t xml:space="preserve">  Total Runs Analyzed: 2  |  Metrics: Relational Accuracy, RIGHT/WRONG Relations, Furniture Overlaps, OBB Overlap Area, Out-of-Bounds, Free Floor %, Walkability</t>
         </is>
       </c>
     </row>
@@ -636,40 +660,60 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Relational Acc (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>RIGHT Relations</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>WRONG Relations</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WRONG Relation Details</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>Overlaps (Count)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>OBB Overlap (m²)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Out of Bounds</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Max OOB Dist (m)</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Free Floor %</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Walkable Components</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Center Clear (m)</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Grade Status</t>
         </is>
@@ -690,41 +734,55 @@
       <c r="D6" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
+      <c r="E6" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2761</v>
+        <v>43</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>None (All Relations RIGHT)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="J6" s="4" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>78.5</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="P6" s="9" t="inlineStr">
         <is>
           <t>EXCELLENT</t>
         </is>
       </c>
     </row>
     <row r="7" ht="115" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>relational_attempt1.txt</t>
         </is>
@@ -732,28 +790,42 @@
       <c r="D7" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>None (All Relations RIGHT)</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="J7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="L7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="M7" s="10" t="n">
         <v>68.2</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="N7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="O7" s="10" t="n">
         <v>0.192</v>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="P7" s="9" t="inlineStr">
         <is>
           <t>EXCELLENT</t>
         </is>
@@ -761,10 +833,3263 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="A1:P2"/>
+    <mergeCell ref="A3:P3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Detailed Spatial Relationship Verification Breakdown (RIGHT vs WRONG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Log File Name</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Source Object (s)</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Relation Type</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Target Object (o)</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Measurement Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.25m³ vs vol_d=1.28m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>dx=-0.675m</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.174m</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>dx=-0.700m</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>dx=-0.693m</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.94m³ vs vol_d=0.25m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>dist=0.675m</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.25m³ vs vol_d=1.94m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.25m³ vs vol_d=1.28m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.94m³ vs vol_d=0.25m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>dist=0.684m</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.157m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.171m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.28m³ vs vol_d=0.25m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.28m³ vs vol_d=1.94m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>dx=-0.682m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>dist=0.700m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.771m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.25m³ vs vol_d=1.94m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.28m³ vs vol_d=0.25m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>dz=+1.154m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.771m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.771m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.771m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>debug_bbox_input_DiningRoom-31158.txt</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.771m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.24m³ vs vol_d=1.48m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.107m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>dz=-0.924m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>dx=-0.597m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.139m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.64m³ vs vol_d=0.24m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>dist=1.203m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.19m³ vs vol_d=1.64m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.19m³ vs vol_d=1.48m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.64m³ vs vol_d=0.22m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>dist=1.493m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.396m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.412m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.48m³ vs vol_d=0.22m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.48m³ vs vol_d=1.64m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>dx=-0.565m</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>dist=0.771m</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.448m</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=0.33m³ vs vol_d=1.64m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>vol_s=1.48m³ vs vol_d=0.33m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>dz=+1.884m</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.444m</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.445m</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.448m</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>relational_attempt1.txt</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>dy=+1.445m</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/debug_bbox2/layout_ranking_report.xlsx
+++ b/debug_bbox2/layout_ranking_report.xlsx
@@ -19,9 +19,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,8 +67,26 @@
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +129,30 @@
         <bgColor rgb="00F9FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6EEF8"/>
+        <bgColor rgb="00E6EEF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -138,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -175,10 +217,29 @@
     <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -299,6 +360,106 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -601,12 +762,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -633,7 +794,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Runs Analyzed: 2  |  Metrics: Relational Accuracy, RIGHT/WRONG Relations, Furniture Overlaps, OBB Overlap Area, Out-of-Bounds, Free Floor %, Walkability</t>
+          <t xml:space="preserve">  Total Runs Analyzed: 6  |  Includes 2 Special Benchmark Rows (Baseline Model &amp; Complete Released Full Model)</t>
         </is>
       </c>
     </row>
@@ -650,7 +811,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Log File Name</t>
+          <t>Log File / Model Name</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -735,17 +896,17 @@
         <v>100</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>None (All Relations RIGHT)</t>
+          <t>lamp(6)--[above]--&gt;chair(2), lamp(6)--[above]--&gt;table(1), lamp(6)--[above]--&gt;chair(3), lamp(6)--[above]--&gt;chair(4), lamp(6)--[above]--&gt;chair(5)</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
@@ -784,24 +945,24 @@
       <c r="B7" s="11" t="n"/>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>relational_attempt1.txt</t>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
         <v>90</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>88</v>
+        <v>0.88</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>None (All Relations RIGHT)</t>
+          <t>chair(2)--[close by]--&gt;chair(3), chair(5)--[close by]--&gt;table(1), table(1)--[smaller than]--&gt;lamp(6), lamp(6)--[above]--&gt;chair(2), lamp(6)--[above]--&gt;table(1), lamp(6)--[above]--&gt;chair(3), lamp(6)--[above]--&gt;chair(4), lamp(6)--[above]--&gt;chair(5)</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
@@ -826,6 +987,230 @@
         <v>0.192</v>
       </c>
       <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="115" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>chair(2)--[close by]--&gt;chair(3), table(1)--[smaller than]--&gt;lamp(6), chair(5)--[close by]--&gt;chair(4), lamp(6)--[above]--&gt;chair(2), lamp(6)--[above]--&gt;table(1), lamp(6)--[above]--&gt;chair(3), lamp(6)--[above]--&gt;chair(4), lamp(6)--[above]--&gt;chair(5)</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>MINOR ISSUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="115" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>chair(2)--[close by]--&gt;chair(3), table(1)--[smaller than]--&gt;lamp(6), chair(5)--[close by]--&gt;chair(4), lamp(6)--[above]--&gt;chair(2), lamp(6)--[above]--&gt;table(1), lamp(6)--[above]--&gt;chair(3), lamp(6)--[above]--&gt;chair(4), lamp(6)--[above]--&gt;chair(5)</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="15" t="inlineStr">
+        <is>
+          <t>MINOR ISSUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="115" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>94.55216741214285</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>0.8370000000000001</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>chair(2)--[close by]--&gt;chair(3), table(1)--[smaller than]--&gt;lamp(6), lamp(6)--[above]--&gt;chair(2), lamp(6)--[above]--&gt;table(1), lamp(6)--[above]--&gt;chair(3), lamp(6)--[above]--&gt;chair(4), lamp(6)--[above]--&gt;chair(5)</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="16" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="N10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="115" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>0.8370000000000001</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>chair(2)--[close by]--&gt;chair(3), chair(5)--[close by]--&gt;chair(4), lamp(6)--[above]--&gt;chair(2), lamp(6)--[above]--&gt;table(1), lamp(6)--[above]--&gt;chair(3), lamp(6)--[above]--&gt;chair(4), lamp(6)--[above]--&gt;chair(5)</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="N11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
         <is>
           <t>EXCELLENT</t>
         </is>
@@ -847,11 +1232,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -868,37 +1253,37 @@
     </row>
     <row r="2"/>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Log File Name</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Log File / Model Name</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Source Object (s)</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Relation Type</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Target Object (o)</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>Measurement Details</t>
         </is>
@@ -910,7 +1295,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -947,7 +1332,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -974,7 +1359,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.25m³ vs vol_d=1.28m³</t>
+          <t>ratio=-4.12 (vol_s=0.25m³ vs vol_o=1.28m³)</t>
         </is>
       </c>
     </row>
@@ -984,7 +1369,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1011,7 +1396,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>dx=-0.675m</t>
+          <t>dx=-0.675m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1406,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1048,7 +1433,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.174m</t>
+          <t>dz=-1.174m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1443,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1085,7 +1470,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>dx=-0.700m</t>
+          <t>dx=-0.700m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1480,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1122,7 +1507,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>dx=-0.693m</t>
+          <t>dx=-0.693m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1517,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1159,7 +1544,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.94m³ vs vol_d=0.25m³</t>
+          <t>ratio=+0.87 (vol_s=1.94m³ vs vol_o=0.25m³)</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1554,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1196,7 +1581,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>dist=0.675m</t>
+          <t>3d_dist=0.073m</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1591,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1233,7 +1618,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.25m³ vs vol_d=1.94m³</t>
+          <t>ratio=-6.80 (vol_s=0.25m³ vs vol_o=1.94m³)</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1628,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1280,7 +1665,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1317,7 +1702,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1344,7 +1729,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.25m³ vs vol_d=1.28m³</t>
+          <t>ratio=-4.12 (vol_s=0.25m³ vs vol_o=1.28m³)</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1739,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1381,7 +1766,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.94m³ vs vol_d=0.25m³</t>
+          <t>ratio=+0.87 (vol_s=1.94m³ vs vol_o=0.25m³)</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1776,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1428,7 +1813,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1455,7 +1840,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>dist=0.684m</t>
+          <t>3d_dist=0.370m</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1850,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1492,7 +1877,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.157m</t>
+          <t>dz=-1.157m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1887,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1539,7 +1924,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1566,7 +1951,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.171m</t>
+          <t>dz=-1.171m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1961,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1613,7 +1998,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1650,7 +2035,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1687,7 +2072,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1724,7 +2109,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1761,7 +2146,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1788,7 +2173,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.28m³ vs vol_d=0.25m³</t>
+          <t>ratio=+0.80 (vol_s=1.28m³ vs vol_o=0.25m³)</t>
         </is>
       </c>
     </row>
@@ -1798,7 +2183,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1835,7 +2220,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1872,7 +2257,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1909,7 +2294,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1936,7 +2321,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.28m³ vs vol_d=1.94m³</t>
+          <t>ratio=-0.52 (vol_s=1.28m³ vs vol_o=1.94m³)</t>
         </is>
       </c>
     </row>
@@ -1946,7 +2331,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -1983,7 +2368,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2020,7 +2405,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2047,7 +2432,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>dx=-0.682m</t>
+          <t>dx=-0.682m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2442,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2084,7 +2469,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>dist=0.700m</t>
+          <t>3d_dist=0.096m</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2479,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2114,14 +2499,14 @@
           <t>chair (2)</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.771m</t>
+          <t>dy=1.771m</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2516,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2158,7 +2543,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.25m³ vs vol_d=1.94m³</t>
+          <t>ratio=-6.80 (vol_s=0.25m³ vs vol_o=1.94m³)</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2553,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2195,7 +2580,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.28m³ vs vol_d=0.25m³</t>
+          <t>ratio=+0.80 (vol_s=1.28m³ vs vol_o=0.25m³)</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2590,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2232,7 +2617,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>dz=+1.154m</t>
+          <t>dz=+1.154m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2627,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2279,7 +2664,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2316,7 +2701,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2336,14 +2721,14 @@
           <t>table (1)</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.771m</t>
+          <t>dy=1.771m</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2738,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2373,14 +2758,14 @@
           <t>chair (3)</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.771m</t>
+          <t>dy=1.771m</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2775,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2427,7 +2812,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2447,14 +2832,14 @@
           <t>chair (4)</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.771m</t>
+          <t>dy=1.771m</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2849,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>debug_bbox_input_DiningRoom-31158.txt</t>
         </is>
@@ -2484,14 +2869,14 @@
           <t>chair (5)</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.771m</t>
+          <t>dy=1.771m</t>
         </is>
       </c>
     </row>
@@ -2501,9 +2886,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2538,9 +2923,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2565,7 +2950,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.24m³ vs vol_d=1.48m³</t>
+          <t>ratio=-5.26 (vol_s=0.24m³ vs vol_o=1.48m³)</t>
         </is>
       </c>
     </row>
@@ -2575,9 +2960,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2602,7 +2987,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>dx=-1.107m</t>
+          <t>dx=-1.107m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2612,9 +2997,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2639,7 +3024,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>dz=-0.924m</t>
+          <t>dz=-0.924m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2649,9 +3034,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2676,7 +3061,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>dx=-0.597m</t>
+          <t>dx=-0.597m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2686,9 +3071,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2713,7 +3098,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>dx=-1.139m</t>
+          <t>dx=-1.139m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -2723,9 +3108,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2750,7 +3135,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.64m³ vs vol_d=0.24m³</t>
+          <t>ratio=+0.86 (vol_s=1.64m³ vs vol_o=0.24m³)</t>
         </is>
       </c>
     </row>
@@ -2760,9 +3145,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2780,14 +3165,14 @@
           <t>chair (3)</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>dist=1.203m</t>
+          <t>3d_dist=0.566m</t>
         </is>
       </c>
     </row>
@@ -2797,9 +3182,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2824,7 +3209,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.19m³ vs vol_d=1.64m³</t>
+          <t>ratio=-7.43 (vol_s=0.19m³ vs vol_o=1.64m³)</t>
         </is>
       </c>
     </row>
@@ -2834,9 +3219,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2871,9 +3256,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -2908,9 +3293,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -2935,7 +3320,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.19m³ vs vol_d=1.48m³</t>
+          <t>ratio=-6.61 (vol_s=0.19m³ vs vol_o=1.48m³)</t>
         </is>
       </c>
     </row>
@@ -2945,9 +3330,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2972,7 +3357,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.64m³ vs vol_d=0.22m³</t>
+          <t>ratio=+0.86 (vol_s=1.64m³ vs vol_o=0.22m³)</t>
         </is>
       </c>
     </row>
@@ -2982,9 +3367,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3019,9 +3404,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3039,14 +3424,14 @@
           <t>table (1)</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F62" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>dist=1.493m</t>
+          <t>3d_dist=0.548m</t>
         </is>
       </c>
     </row>
@@ -3056,9 +3441,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3083,7 +3468,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.396m</t>
+          <t>dz=-1.396m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3093,9 +3478,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B64" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3130,9 +3515,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3157,7 +3542,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>dz=-1.412m</t>
+          <t>dz=-1.412m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3167,9 +3552,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3204,9 +3589,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3241,9 +3626,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3278,9 +3663,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3315,9 +3700,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3352,9 +3737,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3379,7 +3764,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.48m³ vs vol_d=0.22m³</t>
+          <t>ratio=+0.85 (vol_s=1.48m³ vs vol_o=0.22m³)</t>
         </is>
       </c>
     </row>
@@ -3389,9 +3774,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3426,9 +3811,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B73" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3463,9 +3848,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3500,9 +3885,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B75" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3520,14 +3905,14 @@
           <t>lamp (6)</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.48m³ vs vol_d=1.64m³</t>
+          <t>ratio=-0.11 (vol_s=1.48m³ vs vol_o=1.64m³)</t>
         </is>
       </c>
     </row>
@@ -3537,9 +3922,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3574,9 +3959,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3611,9 +3996,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B78" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3638,7 +4023,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>dx=-0.565m</t>
+          <t>dx=-0.565m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3648,9 +4033,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B79" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3675,7 +4060,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>dist=0.771m</t>
+          <t>3d_dist=0.096m</t>
         </is>
       </c>
     </row>
@@ -3685,9 +4070,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B80" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -3705,14 +4090,14 @@
           <t>chair (2)</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F80" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.448m</t>
+          <t>dy=1.448m</t>
         </is>
       </c>
     </row>
@@ -3722,9 +4107,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3749,7 +4134,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>vol_s=0.33m³ vs vol_d=1.64m³</t>
+          <t>ratio=-3.99 (vol_s=0.33m³ vs vol_o=1.64m³)</t>
         </is>
       </c>
     </row>
@@ -3759,9 +4144,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B82" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3786,7 +4171,7 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>vol_s=1.48m³ vs vol_d=0.33m³</t>
+          <t>ratio=+0.78 (vol_s=1.48m³ vs vol_o=0.33m³)</t>
         </is>
       </c>
     </row>
@@ -3796,9 +4181,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B83" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3823,7 +4208,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>dz=+1.884m</t>
+          <t>dz=+1.884m, iou=0.00</t>
         </is>
       </c>
     </row>
@@ -3833,9 +4218,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -3870,9 +4255,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3907,9 +4292,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B86" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -3927,14 +4312,14 @@
           <t>table (1)</t>
         </is>
       </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F86" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.444m</t>
+          <t>dy=1.444m</t>
         </is>
       </c>
     </row>
@@ -3944,9 +4329,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B87" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3964,14 +4349,14 @@
           <t>chair (3)</t>
         </is>
       </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F87" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.445m</t>
+          <t>dy=1.445m</t>
         </is>
       </c>
     </row>
@@ -3981,9 +4366,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B88" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4018,9 +4403,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4038,14 +4423,14 @@
           <t>chair (4)</t>
         </is>
       </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.448m</t>
+          <t>dy=1.448m</t>
         </is>
       </c>
     </row>
@@ -4055,9 +4440,9 @@
           <t>#2</t>
         </is>
       </c>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>relational_attempt1.txt</t>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt1_weight10_v1.txt</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4075,14 +4460,6378 @@
           <t>chair (5)</t>
         </is>
       </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
+      <c r="F90" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>dy=+1.445m</t>
+          <t>dy=1.445m</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-5.20 (vol_s=0.24m³ vs vol_o=1.48m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.819m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>dz=-0.960m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.141m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.821m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>ratio=+0.85 (vol_s=1.59m³ vs vol_o=0.24m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F98" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>3d_dist=1.279m</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B99" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-7.10 (vol_s=0.20m³ vs vol_o=1.59m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B101" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-6.53 (vol_s=0.20m³ vs vol_o=1.48m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>ratio=+0.86 (vol_s=1.59m³ vs vol_o=0.22m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>3d_dist=0.253m</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.086m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B107" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.286m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B111" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B113" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>ratio=+0.85 (vol_s=1.48m³ vs vol_o=0.22m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B115" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B117" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F118" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-0.08 (vol_s=1.48m³ vs vol_o=1.59m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B121" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.139m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B122" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F122" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>3d_dist=0.634m</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B123" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.580m</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-3.79 (vol_s=0.33m³ vs vol_o=1.59m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B125" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>ratio=+0.78 (vol_s=1.48m³ vs vol_o=0.33m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>dz=+1.412m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B127" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B129" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.576m</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F130" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.576m</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B131" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F132" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.580m</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt0_base.txt</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.576m</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B135" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-5.19 (vol_s=0.24m³ vs vol_o=1.48m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.820m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B137" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>dz=-0.957m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.128m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B139" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.819m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>ratio=+0.85 (vol_s=1.60m³ vs vol_o=0.24m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B141" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>3d_dist=1.279m</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-7.12 (vol_s=0.20m³ vs vol_o=1.60m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B143" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B145" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-6.50 (vol_s=0.20m³ vs vol_o=1.48m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>ratio=+0.86 (vol_s=1.60m³ vs vol_o=0.22m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B147" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B148" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>3d_dist=0.244m</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B149" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.079m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B150" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B151" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>dz=-1.293m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B152" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B153" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B154" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B155" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B156" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B157" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>ratio=+0.85 (vol_s=1.48m³ vs vol_o=0.22m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B158" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B159" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B160" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B161" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F161" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-0.08 (vol_s=1.48m³ vs vol_o=1.60m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B162" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B163" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B164" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>dx=-1.129m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B165" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F165" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>3d_dist=0.618m</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B166" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F166" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.567m</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B167" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>ratio=-3.82 (vol_s=0.33m³ vs vol_o=1.60m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B168" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>ratio=+0.78 (vol_s=1.48m³ vs vol_o=0.33m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B169" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>dz=+1.415m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B170" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B171" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B172" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F172" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.563m</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B173" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F173" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.563m</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B174" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B175" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F175" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.567m</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B176" s="20" t="inlineStr">
+        <is>
+          <t>relational_attempt2_weight1_v1.txt</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F176" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>dy=1.563m</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B177" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D177" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E177" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F177" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G177" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B178" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C178" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E178" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G178" s="16" t="inlineStr">
+        <is>
+          <t>ratio=-5.83 (vol_s=0.22m³ vs vol_o=1.48m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B179" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C179" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D179" s="16" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E179" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G179" s="16" t="inlineStr">
+        <is>
+          <t>dx=-1.783m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B180" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E180" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F180" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G180" s="16" t="inlineStr">
+        <is>
+          <t>dz=-0.794m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B181" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C181" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D181" s="16" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E181" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F181" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G181" s="16" t="inlineStr">
+        <is>
+          <t>dx=-0.814m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B182" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E182" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F182" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G182" s="16" t="inlineStr">
+        <is>
+          <t>dx=-1.318m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B183" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C183" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D183" s="16" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E183" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G183" s="16" t="inlineStr">
+        <is>
+          <t>ratio=+0.85 (vol_s=1.42m³ vs vol_o=0.22m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B184" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C184" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E184" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F184" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G184" s="16" t="inlineStr">
+        <is>
+          <t>3d_dist=1.239m</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B185" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C185" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D185" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E185" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F185" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G185" s="16" t="inlineStr">
+        <is>
+          <t>ratio=-5.07 (vol_s=0.23m³ vs vol_o=1.42m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B186" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C186" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D186" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E186" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F186" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G186" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B187" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C187" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D187" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E187" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G187" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B188" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C188" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E188" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F188" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G188" s="16" t="inlineStr">
+        <is>
+          <t>ratio=-5.31 (vol_s=0.23m³ vs vol_o=1.48m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B189" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C189" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D189" s="16" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E189" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G189" s="16" t="inlineStr">
+        <is>
+          <t>ratio=+0.84 (vol_s=1.42m³ vs vol_o=0.22m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B190" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C190" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E190" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G190" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B191" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D191" s="16" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E191" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F191" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G191" s="16" t="inlineStr">
+        <is>
+          <t>3d_dist=0.145m</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B192" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C192" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E192" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F192" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G192" s="16" t="inlineStr">
+        <is>
+          <t>dz=-1.125m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B193" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C193" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D193" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E193" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F193" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G193" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B194" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E194" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F194" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G194" s="16" t="inlineStr">
+        <is>
+          <t>dz=-0.930m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B195" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D195" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E195" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F195" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G195" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B196" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C196" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E196" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F196" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G196" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B197" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C197" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D197" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E197" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F197" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G197" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B198" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C198" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D198" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E198" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F198" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G198" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B199" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C199" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D199" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E199" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F199" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G199" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B200" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C200" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D200" s="16" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E200" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F200" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G200" s="16" t="inlineStr">
+        <is>
+          <t>ratio=+0.85 (vol_s=1.48m³ vs vol_o=0.22m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B201" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C201" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D201" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F201" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G201" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B202" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D202" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E202" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F202" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G202" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B203" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C203" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D203" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E203" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F203" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G203" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B204" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C204" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D204" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E204" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F204" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G204" s="16" t="inlineStr">
+        <is>
+          <t>ratio=+0.04 (vol_s=1.48m³ vs vol_o=1.42m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B205" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C205" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D205" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E205" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F205" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G205" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B206" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C206" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D206" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E206" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F206" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G206" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B207" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C207" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D207" s="16" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E207" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F207" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G207" s="16" t="inlineStr">
+        <is>
+          <t>dx=-1.279m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B208" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C208" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D208" s="16" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E208" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F208" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G208" s="16" t="inlineStr">
+        <is>
+          <t>3d_dist=0.209m</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B209" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C209" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D209" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E209" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F209" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G209" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.572m</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B210" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C210" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D210" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E210" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G210" s="16" t="inlineStr">
+        <is>
+          <t>ratio=-3.14 (vol_s=0.34m³ vs vol_o=1.42m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B211" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C211" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D211" s="16" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E211" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F211" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G211" s="16" t="inlineStr">
+        <is>
+          <t>ratio=+0.77 (vol_s=1.48m³ vs vol_o=0.34m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B212" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C212" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D212" s="16" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E212" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G212" s="16" t="inlineStr">
+        <is>
+          <t>dz=+1.261m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B213" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C213" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D213" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E213" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G213" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B214" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C214" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E214" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G214" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B215" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C215" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D215" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E215" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F215" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G215" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.573m</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B216" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C216" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D216" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E216" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F216" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G216" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.573m</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B217" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C217" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D217" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E217" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G217" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B218" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C218" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D218" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E218" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F218" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G218" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.572m</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B219" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+        </is>
+      </c>
+      <c r="C219" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D219" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E219" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F219" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G219" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.571m</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B220" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C220" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D220" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E220" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F220" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G220" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B221" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C221" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D221" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E221" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F221" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G221" s="16" t="inlineStr">
+        <is>
+          <t>ratio=-3.46 (vol_s=0.20m³ vs vol_o=0.88m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B222" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C222" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D222" s="16" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E222" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F222" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G222" s="16" t="inlineStr">
+        <is>
+          <t>dx=-1.452m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B223" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C223" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D223" s="16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E223" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G223" s="16" t="inlineStr">
+        <is>
+          <t>dz=-0.958m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B224" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C224" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D224" s="16" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E224" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F224" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G224" s="16" t="inlineStr">
+        <is>
+          <t>dx=-1.359m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B225" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C225" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D225" s="16" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E225" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G225" s="16" t="inlineStr">
+        <is>
+          <t>dx=-1.407m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B226" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C226" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D226" s="16" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E226" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G226" s="16" t="inlineStr">
+        <is>
+          <t>ratio=+0.88 (vol_s=1.62m³ vs vol_o=0.20m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B227" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C227" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D227" s="16" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E227" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F227" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G227" s="16" t="inlineStr">
+        <is>
+          <t>3d_dist=0.878m</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B228" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C228" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D228" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E228" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G228" s="16" t="inlineStr">
+        <is>
+          <t>ratio=-5.06 (vol_s=0.27m³ vs vol_o=1.62m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B229" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C229" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D229" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E229" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G229" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B230" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C230" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D230" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E230" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G230" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B231" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C231" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D231" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E231" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G231" s="16" t="inlineStr">
+        <is>
+          <t>ratio=-2.31 (vol_s=0.27m³ vs vol_o=0.88m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B232" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C232" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D232" s="16" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E232" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G232" s="16" t="inlineStr">
+        <is>
+          <t>ratio=+0.83 (vol_s=1.62m³ vs vol_o=0.27m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B233" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C233" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D233" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E233" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G233" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B234" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C234" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D234" s="16" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E234" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G234" s="16" t="inlineStr">
+        <is>
+          <t>3d_dist=0.241m</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B235" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C235" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D235" s="16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E235" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G235" s="16" t="inlineStr">
+        <is>
+          <t>dz=-1.495m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B236" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C236" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D236" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E236" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F236" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G236" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B237" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C237" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D237" s="16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="E237" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G237" s="16" t="inlineStr">
+        <is>
+          <t>dz=-1.227m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B238" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C238" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D238" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E238" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G238" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B239" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C239" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D239" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E239" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G239" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B240" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C240" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D240" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E240" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F240" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G240" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B241" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C241" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D241" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E241" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G241" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B242" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C242" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D242" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E242" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F242" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G242" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B243" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C243" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D243" s="16" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E243" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F243" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G243" s="16" t="inlineStr">
+        <is>
+          <t>ratio=+0.69 (vol_s=0.88m³ vs vol_o=0.27m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B244" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C244" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D244" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E244" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F244" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G244" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B245" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C245" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D245" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E245" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F245" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G245" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B246" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C246" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D246" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E246" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F246" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G246" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B247" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C247" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D247" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E247" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F247" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G247" s="16" t="inlineStr">
+        <is>
+          <t>ratio=-0.83 (vol_s=0.88m³ vs vol_o=1.62m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B248" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C248" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D248" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E248" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G248" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B249" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C249" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D249" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E249" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F249" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G249" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B250" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C250" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D250" s="16" t="inlineStr">
+        <is>
+          <t>behind</t>
+        </is>
+      </c>
+      <c r="E250" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G250" s="16" t="inlineStr">
+        <is>
+          <t>dx=-1.403m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B251" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C251" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D251" s="16" t="inlineStr">
+        <is>
+          <t>close by</t>
+        </is>
+      </c>
+      <c r="E251" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F251" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G251" s="16" t="inlineStr">
+        <is>
+          <t>3d_dist=0.773m</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B252" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C252" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D252" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E252" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F252" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G252" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.529m</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B253" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C253" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="D253" s="16" t="inlineStr">
+        <is>
+          <t>smaller than</t>
+        </is>
+      </c>
+      <c r="E253" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="F253" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G253" s="16" t="inlineStr">
+        <is>
+          <t>ratio=-3.61 (vol_s=0.35m³ vs vol_o=1.62m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B254" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C254" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="D254" s="16" t="inlineStr">
+        <is>
+          <t>bigger than</t>
+        </is>
+      </c>
+      <c r="E254" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F254" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G254" s="16" t="inlineStr">
+        <is>
+          <t>ratio=+0.60 (vol_s=0.88m³ vs vol_o=0.35m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B255" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C255" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="D255" s="16" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="E255" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F255" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G255" s="16" t="inlineStr">
+        <is>
+          <t>dz=+1.763m, iou=0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B256" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C256" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="D256" s="16" t="inlineStr">
+        <is>
+          <t>same super category as</t>
+        </is>
+      </c>
+      <c r="E256" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F256" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G256" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B257" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C257" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D257" s="16" t="inlineStr">
+        <is>
+          <t>same material as</t>
+        </is>
+      </c>
+      <c r="E257" s="16" t="inlineStr">
+        <is>
+          <t>chair (2)</t>
+        </is>
+      </c>
+      <c r="F257" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G257" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B258" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C258" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D258" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E258" s="16" t="inlineStr">
+        <is>
+          <t>table (1)</t>
+        </is>
+      </c>
+      <c r="F258" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G258" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.557m</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B259" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C259" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D259" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E259" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F259" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G259" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.532m</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B260" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C260" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="D260" s="16" t="inlineStr">
+        <is>
+          <t>same style as</t>
+        </is>
+      </c>
+      <c r="E260" s="16" t="inlineStr">
+        <is>
+          <t>chair (3)</t>
+        </is>
+      </c>
+      <c r="F260" s="9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="G260" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B261" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C261" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D261" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E261" s="16" t="inlineStr">
+        <is>
+          <t>chair (4)</t>
+        </is>
+      </c>
+      <c r="F261" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G261" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.537m</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="16" t="inlineStr">
+        <is>
+          <t>[BENCHMARK]</t>
+        </is>
+      </c>
+      <c r="B262" s="22" t="inlineStr">
+        <is>
+          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+        </is>
+      </c>
+      <c r="C262" s="16" t="inlineStr">
+        <is>
+          <t>lamp (6)</t>
+        </is>
+      </c>
+      <c r="D262" s="16" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E262" s="16" t="inlineStr">
+        <is>
+          <t>chair (5)</t>
+        </is>
+      </c>
+      <c r="F262" s="21" t="inlineStr">
+        <is>
+          <t>WRONG</t>
+        </is>
+      </c>
+      <c r="G262" s="16" t="inlineStr">
+        <is>
+          <t>dy=1.536m</t>
         </is>
       </c>
     </row>

--- a/debug_bbox2/layout_ranking_report.xlsx
+++ b/debug_bbox2/layout_ranking_report.xlsx
@@ -1113,7 +1113,7 @@
       <c r="B10" s="17" t="n"/>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
@@ -1169,7 +1169,7 @@
       <c r="B11" s="17" t="n"/>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="B177" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C177" s="16" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="B178" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C178" s="16" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B179" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C179" s="16" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B180" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C180" s="16" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="B181" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C181" s="16" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="B182" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C182" s="16" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B183" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C183" s="16" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="B184" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C184" s="16" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="B185" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C185" s="16" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B186" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C186" s="16" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="B187" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C187" s="16" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B188" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C188" s="16" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="B189" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C189" s="16" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="B190" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C190" s="16" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="B191" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C191" s="16" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="B192" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C192" s="16" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="B193" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C193" s="16" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="B194" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C194" s="16" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B195" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C195" s="16" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="B196" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C196" s="16" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="B197" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C197" s="16" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="B198" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C198" s="16" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="B199" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C199" s="16" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="B200" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C200" s="16" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="B201" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C201" s="16" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B202" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C202" s="16" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="B203" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C203" s="16" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="B204" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C204" s="16" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B205" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C205" s="16" t="inlineStr">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="B206" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C206" s="16" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="B207" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C207" s="16" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B208" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C208" s="16" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="B209" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C209" s="16" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="B210" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C210" s="16" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="B211" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C211" s="16" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="B212" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C212" s="16" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="B213" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C213" s="16" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="B214" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C214" s="16" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="B215" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C215" s="16" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="B216" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C216" s="16" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="B217" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C217" s="16" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="B218" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C218" s="16" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="B219" s="22" t="inlineStr">
         <is>
-          <t>⭐ [BASELINE MODEL] Physcene Collision Resolved</t>
+          <t>[BASELINE MODEL] Physcene Collision Resolved</t>
         </is>
       </c>
       <c r="C219" s="16" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="B220" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C220" s="16" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="B221" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C221" s="16" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="B222" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C222" s="16" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="B223" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C223" s="16" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="B224" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C224" s="16" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="B225" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C225" s="16" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B226" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C226" s="16" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="B227" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C227" s="16" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="B228" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C228" s="16" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="B229" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C229" s="16" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="B230" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C230" s="16" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="B231" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C231" s="16" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B232" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C232" s="16" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="B233" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C233" s="16" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="B234" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C234" s="16" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="B235" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C235" s="16" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="B236" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C236" s="16" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="B237" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C237" s="16" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="B238" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C238" s="16" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="B239" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C239" s="16" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="B240" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C240" s="16" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="B241" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C241" s="16" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="B242" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C242" s="16" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="B243" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C243" s="16" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="B244" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C244" s="16" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="B245" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C245" s="16" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="B246" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C246" s="16" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="B247" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C247" s="16" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="B248" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C248" s="16" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="B249" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C249" s="16" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="B250" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C250" s="16" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="B251" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C251" s="16" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="B252" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C252" s="16" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="B253" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C253" s="16" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B254" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C254" s="16" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="B255" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C255" s="16" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B256" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C256" s="16" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="B257" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C257" s="16" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="B258" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C258" s="16" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B259" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C259" s="16" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="B260" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C260" s="16" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="B261" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C261" s="16" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B262" s="22" t="inlineStr">
         <is>
-          <t>⭐ [RELEASED FULL MODEL] Complete Released Model Resolved</t>
+          <t>[RELEASED FULL MODEL] Complete Released Model Resolved</t>
         </is>
       </c>
       <c r="C262" s="16" t="inlineStr">
